--- a/SGC-CKN/Excel/974671f8-a473-4034-8f2d-e3166fe133af_Thanh_Hoá_P1-06_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/974671f8-a473-4034-8f2d-e3166fe133af_Thanh_Hoá_P1-06_D800_05-04-2026.xlsx
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:15
-04/04/2026</t>
+05/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -165,7 +165,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">01:52
+    <t xml:space="preserve">01:58
 05/04/2026</t>
   </si>
   <si>
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -285,12 +285,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -308,7 +302,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,12 +351,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -373,11 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -478,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -531,17 +520,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,22 +553,19 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1273,53 +1259,53 @@
         <v>-8.7</v>
       </c>
       <c r="G14" s="15">
-        <v>13</v>
+        <v>-13</v>
       </c>
       <c r="H14" s="15">
         <v>0.92</v>
       </c>
       <c r="I14" s="15">
-        <v>21.7</v>
-      </c>
-      <c r="J14" s="18">
-        <v>23.67</v>
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="8">
+        <v>4.69</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-13</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-20.2</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>1.17</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>7.2</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="21">
         <v>6.17</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1351,7 +1337,7 @@
       <c r="I16" s="22">
         <v>5.8</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="21">
         <v>5.8</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1381,67 +1367,67 @@
         <v>-39.5</v>
       </c>
       <c r="H17" s="25">
-        <v>25.62</v>
+        <v>1.72</v>
       </c>
       <c r="I17" s="25">
         <v>13.5</v>
       </c>
-      <c r="J17" s="28">
-        <v>0.53</v>
+      <c r="J17" s="21">
+        <v>7.86</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-39.5</v>
       </c>
-      <c r="G18" s="29">
-        <v>-42.44</v>
-      </c>
-      <c r="H18" s="29">
-        <v>4.63</v>
-      </c>
-      <c r="I18" s="29">
-        <v>2.94</v>
-      </c>
-      <c r="J18" s="28">
-        <v>0.63</v>
-      </c>
-      <c r="K18" s="30" t="s">
+      <c r="G18" s="28">
+        <v>-44.44</v>
+      </c>
+      <c r="H18" s="28">
+        <v>4.53</v>
+      </c>
+      <c r="I18" s="28">
+        <v>4.94</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.09</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1667,44 +1653,44 @@
         <v>-8.7</v>
       </c>
       <c r="F5" s="15">
-        <v>13</v>
+        <v>-13</v>
       </c>
       <c r="G5" s="15">
         <v>0.92</v>
       </c>
       <c r="H5" s="15">
-        <v>21.7</v>
-      </c>
-      <c r="I5" s="18">
-        <v>23.67</v>
+        <v>4.3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4.69</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-13</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-20.2</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>1.17</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>7.2</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="21">
         <v>6.17</v>
       </c>
     </row>
@@ -1733,7 +1719,7 @@
       <c r="H7" s="22">
         <v>5.8</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="21">
         <v>5.8</v>
       </c>
     </row>
@@ -1757,71 +1743,71 @@
         <v>-39.5</v>
       </c>
       <c r="G8" s="25">
-        <v>25.62</v>
+        <v>1.72</v>
       </c>
       <c r="H8" s="25">
         <v>13.5</v>
       </c>
-      <c r="I8" s="28">
-        <v>0.53</v>
+      <c r="I8" s="21">
+        <v>7.86</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-39.5</v>
       </c>
-      <c r="F9" s="29">
-        <v>-42.44</v>
-      </c>
-      <c r="G9" s="29">
-        <v>4.63</v>
-      </c>
-      <c r="H9" s="29">
-        <v>2.94</v>
-      </c>
-      <c r="I9" s="28">
-        <v>0.63</v>
+      <c r="F9" s="28">
+        <v>-44.44</v>
+      </c>
+      <c r="G9" s="28">
+        <v>4.53</v>
+      </c>
+      <c r="H9" s="28">
+        <v>4.94</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
-        <v>-42.44</v>
-      </c>
-      <c r="G10" s="34">
-        <v>37.33</v>
-      </c>
-      <c r="H10" s="34">
-        <v>59.84</v>
-      </c>
-      <c r="I10" s="34">
-        <v>1.6</v>
+      <c r="F10" s="33">
+        <v>-44.44</v>
+      </c>
+      <c r="G10" s="33">
+        <v>13.33</v>
+      </c>
+      <c r="H10" s="33">
+        <v>44.44</v>
+      </c>
+      <c r="I10" s="33">
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
